--- a/main/ig/FRSectionImagingSupportingInformationLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionImagingSupportingInformationLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:36:17+00:00</t>
+    <t>2026-09-28T10:07:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionImagingSupportingInformationLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionImagingSupportingInformationLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:07:47+00:00</t>
+    <t>2026-09-30T20:10:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRSectionImagingSupportingInformationLMCDAFHIR.xlsx
+++ b/main/ig/FRSectionImagingSupportingInformationLMCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:10:21+00:00</t>
+    <t>2026-10-08T12:56:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
